--- a/public/samples/bulk-review-requests-sample.xlsx
+++ b/public/samples/bulk-review-requests-sample.xlsx
@@ -1,44 +1,124 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10703"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/johntang/Desktop/clients/baam-review/public/samples/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE4CF9EA-2848-5E4C-809C-973BAA1A0242}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="Customers" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="27">
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>Phone</t>
+  </si>
+  <si>
+    <t>Language</t>
+  </si>
+  <si>
+    <t>Visit date</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>Marcus Davis</t>
+  </si>
+  <si>
+    <t>English</t>
+  </si>
+  <si>
+    <t>2026-05-05</t>
+  </si>
+  <si>
+    <t>chronic migraines</t>
+  </si>
+  <si>
+    <t>Linda Chen</t>
+  </si>
+  <si>
+    <t>中文</t>
+  </si>
+  <si>
+    <t>2026-05-06</t>
+  </si>
+  <si>
+    <t>first visit</t>
+  </si>
+  <si>
+    <t>张伟</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Chinese</t>
+  </si>
+  <si>
+    <t>2026-05-07</t>
+  </si>
+  <si>
+    <t>returning patient</t>
+  </si>
+  <si>
+    <t>2026-05-08</t>
+  </si>
+  <si>
+    <t>Patrick O'Connor</t>
+  </si>
+  <si>
+    <t>patrick.o@example.com</t>
+  </si>
+  <si>
+    <t>(845)238-1767</t>
+  </si>
+  <si>
+    <t>(201) 785-7763</t>
+  </si>
+  <si>
+    <t>john.tang2025@gmail.com</t>
+  </si>
+  <si>
+    <t>baamplatform@gmail.com</t>
+  </si>
+  <si>
+    <t>support@baamplatform.com</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -61,17 +141,28 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -396,140 +487,126 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18.83203125" customWidth="1"/>
     <col min="2" max="2" width="28.83203125" customWidth="1"/>
     <col min="3" max="3" width="18.83203125" customWidth="1"/>
-    <col min="4" max="4" width="12.83203125" customWidth="1"/>
-    <col min="5" max="5" width="12.83203125" customWidth="1"/>
+    <col min="4" max="5" width="12.83203125" customWidth="1"/>
     <col min="6" max="6" width="32.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Name</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Email</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Phone</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Language</v>
-      </c>
-      <c r="E1" t="str">
-        <v>Visit date</v>
-      </c>
-      <c r="F1" t="str">
-        <v>Notes</v>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>Marcus Davis</v>
-      </c>
-      <c r="B2" t="str">
-        <v>marcus.d@gmail.com</v>
-      </c>
-      <c r="C2" t="str">
-        <v>(917) 555-0234</v>
-      </c>
-      <c r="D2" t="str">
-        <v>English</v>
-      </c>
-      <c r="E2" t="str">
-        <v>2026-05-05</v>
-      </c>
-      <c r="F2" t="str">
-        <v>chronic migraines</v>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>Linda Chen</v>
-      </c>
-      <c r="B3" t="str">
-        <v>linda.chen@example.com</v>
-      </c>
-      <c r="C3" t="str">
-        <v>(718) 555-0188</v>
-      </c>
-      <c r="D3" t="str">
-        <v>中文</v>
-      </c>
-      <c r="E3" t="str">
-        <v>2026-05-06</v>
-      </c>
-      <c r="F3" t="str">
-        <v>first visit</v>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" t="s">
+        <v>13</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>张伟</v>
-      </c>
-      <c r="B4" t="str">
-        <v>zhangwei2025@example.com</v>
-      </c>
-      <c r="C4" t="str">
-        <v/>
-      </c>
-      <c r="D4" t="str">
-        <v>Chinese</v>
-      </c>
-      <c r="E4" t="str">
-        <v>2026-05-07</v>
-      </c>
-      <c r="F4" t="str">
-        <v>returning patient</v>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F4" t="s">
+        <v>18</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>Sofia Ramirez</v>
-      </c>
-      <c r="B5" t="str">
-        <v/>
-      </c>
-      <c r="C5" t="str">
-        <v>(347) 555-0421</v>
-      </c>
-      <c r="D5" t="str">
-        <v>Spanish</v>
-      </c>
-      <c r="E5" t="str">
-        <v>2026-05-08</v>
-      </c>
-      <c r="F5" t="str">
-        <v>phone only — SMS preferred</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>Patrick O'Connor</v>
-      </c>
-      <c r="B6" t="str">
-        <v>patrick.o@example.com</v>
-      </c>
-      <c r="C6" t="str">
-        <v>(212) 555-0179</v>
-      </c>
-      <c r="D6" t="str">
-        <v>English</v>
-      </c>
-      <c r="E6" t="str">
-        <v>2026-05-08</v>
-      </c>
-      <c r="F6" t="str">
-        <v/>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F5" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B2" r:id="rId1" xr:uid="{CA616226-9AD2-BB4E-8A00-DF800908C119}"/>
+    <hyperlink ref="B3" r:id="rId2" xr:uid="{4757F7B7-2829-124C-B1FA-956A33A283CB}"/>
+    <hyperlink ref="B4" r:id="rId3" xr:uid="{FD9DA321-F244-024A-9F6A-748C8BC649C0}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F6"/>
+    <ignoredError sqref="A1:F1 A5:B5 A2 D2:F2 A3 D3:F3 A4 D4:F4 D5:F5" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>